--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722840.242433592</v>
+        <v>722840</v>
       </c>
       <c r="R2" t="n">
-        <v>6380139.753528076</v>
+        <v>6380140</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1987-06-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722840.242433592</v>
+        <v>722840</v>
       </c>
       <c r="R3" t="n">
-        <v>6380139.753528076</v>
+        <v>6380140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>1987-06-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>105123</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722739.3988845999</v>
+        <v>722739</v>
       </c>
       <c r="R4" t="n">
-        <v>6380188.594628487</v>
+        <v>6380189</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,19 +965,9 @@
           <t>1987-06-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105519</v>
+        <v>105528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107549</v>
+        <v>107558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105528</v>
+        <v>105540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107558</v>
+        <v>107570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105540</v>
+        <v>105549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107570</v>
+        <v>107579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105549</v>
+        <v>105552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107579</v>
+        <v>107584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105552</v>
+        <v>105580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107584</v>
+        <v>107612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105580</v>
+        <v>105586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107612</v>
+        <v>107618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105586</v>
+        <v>105593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107618</v>
+        <v>107625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105593</v>
+        <v>105597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107625</v>
+        <v>107629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105597</v>
+        <v>105604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107629</v>
+        <v>107637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105607</v>
+        <v>105612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107640</v>
+        <v>107645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30490-2025 artfynd.xlsx
+++ b/artfynd/A 30490-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106450870</v>
       </c>
       <c r="B2" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>106450871</v>
       </c>
       <c r="B3" t="n">
-        <v>105612</v>
+        <v>105620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>106450866</v>
       </c>
       <c r="B4" t="n">
-        <v>107645</v>
+        <v>107653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
